--- a/artfynd/A 726-2024 artfynd.xlsx
+++ b/artfynd/A 726-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 726-2024 artfynd.xlsx
+++ b/artfynd/A 726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121724359</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109993</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rytterslyckan, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>423359</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6181573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hörby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östraby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1997-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1997-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Alskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 726-2024 artfynd.xlsx
+++ b/artfynd/A 726-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64568692</v>
+        <v>121724359</v>
       </c>
       <c r="B2" t="n">
-        <v>56812</v>
+        <v>110029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>221049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tollstorp., Sk</t>
+          <t>Rytterslyckan, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423544.8919265489</v>
+        <v>423359</v>
       </c>
       <c r="R2" t="n">
-        <v>6181617.059485289</v>
+        <v>6181573</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +743,24 @@
           <t>Östraby</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Hby-0160</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +772,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Alskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -780,17 +785,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64568687</v>
+        <v>64568692</v>
       </c>
       <c r="B3" t="n">
-        <v>55803</v>
+        <v>56812</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64568689</v>
+        <v>64568687</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
+        <v>55803</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121724359</v>
+        <v>64568689</v>
       </c>
       <c r="B5" t="n">
-        <v>110029</v>
+        <v>57064</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1032,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221049</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rytterslyckan, Småvänderot, Sk</t>
+          <t>Tollstorp., Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423359</v>
+        <v>423544.8919265489</v>
       </c>
       <c r="R5" t="n">
-        <v>6181573</v>
+        <v>6181617.059485289</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,24 +1088,24 @@
           <t>Östraby</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>M-Hby-0160</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1997-08-13</t>
+          <t>2017-03-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1997-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>2017-03-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,11 +1117,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Alskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1121,14 +1125,10 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Wendt</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
